--- a/Helmoltz v3/input/input_parameters.xlsx
+++ b/Helmoltz v3/input/input_parameters.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20392"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11011"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694DB306-F898-4EF0-8023-DC715B80002F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CEA2DF7-30EF-F049-B3BC-087BD02FF794}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="840" yWindow="500" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -302,7 +302,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -581,16 +581,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="17.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="20.28515625" style="3" customWidth="1"/>
-    <col min="5" max="10" width="17.7109375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="18.42578125" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="3" width="17.6640625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="20.33203125" style="3" customWidth="1"/>
+    <col min="5" max="10" width="17.6640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="18.5" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>21</v>
       </c>
@@ -605,7 +605,7 @@
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
     </row>
-    <row r="2" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
@@ -640,7 +640,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -675,7 +675,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>6.7000000000000002E-3</v>
       </c>
@@ -710,12 +710,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="E6" s="10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="5" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" s="5" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>29</v>
       </c>
@@ -737,7 +737,7 @@
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
     </row>
-    <row r="8" spans="1:11" s="5" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" s="5" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>22</v>
       </c>
@@ -757,7 +757,7 @@
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
     </row>
-    <row r="9" spans="1:11" s="5" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" s="5" customFormat="1" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>25</v>
       </c>
@@ -777,7 +777,7 @@
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>30</v>
       </c>
@@ -794,7 +794,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>33</v>
       </c>
